--- a/sheets/조재수대금교본/검수/아리랑 (2).xlsx
+++ b/sheets/조재수대금교본/검수/아리랑 (2).xlsx
@@ -2407,35 +2407,33 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㄱ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧·</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -2596,11 +2594,7 @@
         </is>
       </c>
       <c r="S6" s="22"/>
-      <c r="T6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T6" s="21"/>
       <c r="U6" s="22"/>
     </row>
     <row r="7" ht="141.86" customHeight="true">
@@ -2743,17 +2737,9 @@
     </row>
     <row r="10" ht="141.86" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -2776,8 +2762,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="M10" s="22"/>
@@ -2790,22 +2775,13 @@
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="Q10" s="22"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="22"/>
-      <c r="T10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T10" s="21"/>
       <c r="U10" s="22"/>
     </row>
     <row r="11" ht="141.86" customHeight="true">
@@ -2881,11 +2857,7 @@
       <c r="Q14" s="22"/>
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧</t>
-        </is>
-      </c>
+      <c r="T14" s="21"/>
       <c r="U14" s="22"/>
     </row>
     <row r="15" ht="141.86" customHeight="true">

--- a/sheets/조재수대금교본/검수/아리랑 (2).xlsx
+++ b/sheets/조재수대금교본/검수/아리랑 (2).xlsx
@@ -2407,13 +2407,13 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㄱ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -2426,7 +2426,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">∧·</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -2857,7 +2857,11 @@
       <c r="Q14" s="22"/>
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
-      <c r="T14" s="21"/>
+      <c r="T14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧</t>
+        </is>
+      </c>
       <c r="U14" s="22"/>
     </row>
     <row r="15" ht="141.86" customHeight="true">

--- a/sheets/조재수대금교본/검수/아리랑 (2).xlsx
+++ b/sheets/조재수대금교본/검수/아리랑 (2).xlsx
@@ -2339,32 +2339,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="141.86" customHeight="true">
+    <row r="3" ht="158.96" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="141.86" customHeight="true">
+    <row r="4" ht="158.96" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="22"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="141.86" customHeight="true">
+    <row r="5" ht="158.96" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -2551,7 +2551,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="141.86" customHeight="true">
+    <row r="6" ht="158.96" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -2597,7 +2597,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="141.86" customHeight="true">
+    <row r="7" ht="158.96" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="141.86" customHeight="true">
+    <row r="8" ht="158.96" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="22"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="141.86" customHeight="true">
+    <row r="9" ht="158.96" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2735,7 +2735,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="141.86" customHeight="true">
+    <row r="10" ht="158.96" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -2784,7 +2784,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="141.86" customHeight="true">
+    <row r="11" ht="158.96" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -2810,7 +2810,7 @@
     <row r="12" ht="6.0" customHeight="true">
       <c r="A12" s="0"/>
     </row>
-    <row r="13" ht="71.43" customHeight="true">
+    <row r="13" ht="80.0" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       <c r="T13" s="20"/>
       <c r="U13" s="20"/>
     </row>
-    <row r="14" ht="141.86" customHeight="true">
+    <row r="14" ht="158.96" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="141.86" customHeight="true">
+    <row r="15" ht="158.96" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="141.86" customHeight="true">
+    <row r="16" ht="158.96" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -2914,7 +2914,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="141.86" customHeight="true">
+    <row r="17" ht="158.96" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -2937,7 +2937,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="141.86" customHeight="true">
+    <row r="18" ht="158.96" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -2960,7 +2960,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="141.86" customHeight="true">
+    <row r="19" ht="158.96" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -2983,7 +2983,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="141.86" customHeight="true">
+    <row r="20" ht="158.96" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -3006,7 +3006,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="141.86" customHeight="true">
+    <row r="21" ht="158.96" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -3029,7 +3029,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="141.86" customHeight="true">
+    <row r="22" ht="158.96" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
@@ -3059,7 +3059,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="11" max="16383" man="1"/>
   </rowBreaks>
